--- a/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL - MANUYO CAMPUS.xlsx
+++ b/excel-files/LAS PINAS/LAS PIÑAS CITY NATIONAL SENIOR HIGH SCHOOL - MANUYO CAMPUS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BEA4DBE-B12E-4088-82E2-89EDB09D61EC}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CD3FED4-CFD7-4C92-9EEC-FB05A0C68AC7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+    <row r="6" spans="1:8" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3607,10 +3607,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="15">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="19.5">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3712,10 +3712,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="15">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="19.5">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="15">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5403,12 +5403,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E93" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E61:E69 E81:E89 E71:E79 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E2:E6 E8:E12 E91:E92 E94:E98" xr:uid="{85DD4C70-DE48-46D4-8D38-1AED99D46A93}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5645,7 +5648,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5714,7 +5717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5783,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5852,7 +5855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -5921,7 +5924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -5990,7 +5993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6059,7 +6062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6128,7 +6131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6210,7 +6213,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6279,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6348,7 +6351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6417,7 +6420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6486,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6555,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6624,7 +6627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6693,7 +6696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6762,7 +6765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6776,7 +6779,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6845,7 +6848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -6914,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -6983,7 +6986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7052,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7121,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7190,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7259,7 +7262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7328,7 +7331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7397,7 +7400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7411,7 +7414,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7480,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7549,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7618,7 +7621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7687,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7756,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7825,7 +7828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -7894,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -7963,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8032,7 +8035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8046,7 +8049,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8115,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8184,7 +8187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8253,7 +8256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8322,7 +8325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8391,7 +8394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8460,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8529,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8598,7 +8601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8667,7 +8670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8681,7 +8684,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8750,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8819,7 +8822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -8888,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -8957,7 +8960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9026,7 +9029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9095,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9164,7 +9167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9233,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9385,7 +9388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9454,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9523,7 +9526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9592,7 +9595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9661,7 +9664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9730,7 +9733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9799,7 +9802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -9868,7 +9871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -9937,7 +9940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -9951,7 +9954,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10020,7 +10023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10089,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10158,7 +10161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10227,7 +10230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10296,7 +10299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10365,7 +10368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10434,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10503,7 +10506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10572,7 +10575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10586,7 +10589,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10655,7 +10658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10724,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10793,7 +10796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10862,7 +10865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -10931,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11000,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11069,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11138,7 +11141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11207,7 +11210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11221,7 +11224,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11290,7 +11293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11359,7 +11362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11428,7 +11431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11497,7 +11500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11566,7 +11569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11635,7 +11638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11704,7 +11707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11773,7 +11776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12218,7 +12221,9 @@
         <v>1800</v>
       </c>
       <c r="K107" s="5"/>
-      <c r="L107" s="1"/>
+      <c r="L107" s="1">
+        <v>2025</v>
+      </c>
       <c r="M107" s="5"/>
       <c r="N107" s="5">
         <f t="shared" si="16"/>
@@ -12496,7 +12501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12507,7 +12512,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12569,7 +12574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12631,7 +12636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12693,7 +12698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12755,7 +12760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12817,7 +12822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12879,7 +12884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12941,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13003,7 +13008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13065,7 +13070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13127,7 +13132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13189,7 +13194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13251,7 +13256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13313,7 +13318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13375,7 +13380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13437,13 +13442,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -13458,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -13485,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -13679,7 +13684,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 H33:I41 H43:I51 H53:I61 H63:I71 H73:I81 H83:I91 H93:I101 H103:I110 Q103:R110 H112:I127 N127:R127 H14:I21 H23:I31 H6:I12 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D63:F71 D93:F101 D83:F91 D73:F81 D53:F61 D43:F51 D33:F41 D23:F31 D14:F21 D103:F110 D112:F127 K6:L12 K63:L71 K93:L101 K83:L91 K73:L81 K53:L61 K43:L51 K33:L41 K23:L31 K14:L21 K103:L110 K112:L127 N5:R12 Q63:R71 Q93:R101 Q83:R91 Q73:R81 Q53:R61 Q43:R51 Q33:R41 Q23:R31 Q14:R21 T5:X12 W63:X71 W103:X110 W112:X127 W93:X101 W83:X91 W73:X81 W53:X61 W43:X51 W33:X41 W23:X31 W14:X21" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -13689,15 +13694,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R112:R127 R103:R110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F73:F81 F93:F101 F83:F91 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F5:F12 F14:F21 F103:F110 F112:F127 L73:L81 L93:L101 L83:L91 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L5:L12 L14:L21 L103:L110 L112:L127 R73:R81 R93:R101 R83:R91 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R5:R12 R14:R21 X73:X81 X112:X127 X103:X110 X93:X101 X83:X91 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X5:X12 X14:X21" xr:uid="{59997D90-2F64-4048-8900-D52A39895EC3}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13719,10 +13727,11 @@
     <col min="2" max="2" width="27.85546875" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
+    <col min="9" max="9" width="42.85546875" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" customWidth="1"/>
     <col min="11" max="11" width="24.42578125" customWidth="1"/>
     <col min="12" max="12" width="18.140625" customWidth="1"/>
@@ -13858,7 +13867,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13927,7 +13936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13996,7 +14005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14065,7 +14074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14134,7 +14143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14203,7 +14212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14272,7 +14281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14341,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14410,8 +14419,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14480,7 +14489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14549,7 +14558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14618,7 +14627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14687,7 +14696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14756,7 +14765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14825,7 +14834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14894,7 +14903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14963,8 +14972,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15033,7 +15042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15102,7 +15111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15171,7 +15180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15240,7 +15249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15309,7 +15318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15378,7 +15387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15447,7 +15456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15516,7 +15525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15585,8 +15594,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15655,7 +15664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15724,7 +15733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15793,7 +15802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15862,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15931,7 +15940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16000,7 +16009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16069,7 +16078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16138,7 +16147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16207,7 +16216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16276,7 +16285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16345,8 +16354,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16415,7 +16424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16484,7 +16493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16553,7 +16562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16622,7 +16631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16691,7 +16700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16760,7 +16769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16829,7 +16838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16898,7 +16907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16967,7 +16976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17036,7 +17045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17105,8 +17114,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17175,7 +17184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17244,7 +17253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17313,7 +17322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17382,7 +17391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17451,7 +17460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17520,7 +17529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17589,7 +17598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17658,7 +17667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17727,7 +17736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -17796,7 +17805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17866,7 +17875,7 @@
       </c>
     </row>
     <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="19.5">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17935,7 +17944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18004,7 +18013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18073,7 +18082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18142,7 +18151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18211,7 +18220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18280,7 +18289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18349,7 +18358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18418,7 +18427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18487,7 +18496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18556,7 +18565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18625,8 +18634,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18695,7 +18704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18764,7 +18773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18833,7 +18842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18902,7 +18911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18971,7 +18980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19040,7 +19049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19109,7 +19118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19178,7 +19187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19247,7 +19256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19316,7 +19325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19385,8 +19394,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19455,7 +19464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.149999999999999">
+    <row r="92" spans="1:27" ht="19.5">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19524,7 +19533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="19.5">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19593,7 +19602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19662,7 +19671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19731,7 +19740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19800,7 +19809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -19869,7 +19878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19938,7 +19947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20007,7 +20016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20076,7 +20085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20145,8 +20154,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20215,7 +20224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20284,7 +20293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20353,7 +20362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20422,7 +20431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.149999999999999">
+    <row r="107" spans="1:27" ht="19.5">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20491,7 +20500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="19.5">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20560,7 +20569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.149999999999999">
+    <row r="109" spans="1:27" ht="19.5">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20629,7 +20638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.149999999999999">
+    <row r="110" spans="1:27" ht="19.5">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20698,7 +20707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.149999999999999">
+    <row r="111" spans="1:27" ht="19.5">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20767,7 +20776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="19.5">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -20836,7 +20845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.149999999999999">
+    <row r="113" spans="1:28" ht="19.5">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21221,7 +21230,9 @@
         <v>1800</v>
       </c>
       <c r="E119" s="5"/>
-      <c r="F119" s="1"/>
+      <c r="F119" s="1">
+        <v>2025</v>
+      </c>
       <c r="G119" s="5"/>
       <c r="H119" s="5">
         <f t="shared" si="22"/>
@@ -21236,7 +21247,9 @@
         <v>1800</v>
       </c>
       <c r="K119" s="5"/>
-      <c r="L119" s="1"/>
+      <c r="L119" s="1">
+        <v>2025</v>
+      </c>
       <c r="M119" s="5"/>
       <c r="N119" s="5">
         <f t="shared" si="20"/>
@@ -22192,7 +22205,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D2:F10 D67:F77 D103:F113 D91:F101 D79:F89 D55:F65 D43:F53 D31:F41 D21:F29 D12:F19 D115:F122 H3:L10 H55:L65 H43:L53 H31:L41 H21:L29 H12:L19 H67:L77 H103:L113 H91:L101 H79:L89 H115:L122 P2:R10 N67:R77 N103:R113 N91:R101 N79:R89 N55:R65 N43:R53 N31:R41 N21:R29 N12:R19 N115:R122 V2:X10 T67:X77 T103:X113 T91:X101 T79:X89 T55:X65 T43:X53 T31:X41 T21:X29 T12:X19 T115:X122" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22202,12 +22215,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F79:F89 F103:F113 F91:F101 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F3:F10 F12:F19 F115:F122 L55:L65 L43:L53 L31:L41 L21:L29 L3:L10 L12:L19 L103:L113 L91:L101 L67:L77 L79:L89 L115:L122 R79:R89 R103:R113 R91:R101 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R3:R10 R12:R19 R115:R122 X79:X89 X103:X113 X91:X101 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X3:X10 X12:X19" xr:uid="{882A9E64-8012-4071-88E9-6C607BFDBA2C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
